--- a/artfynd/A 35937-2023 artfynd.xlsx
+++ b/artfynd/A 35937-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35937-2023 artfynd.xlsx
+++ b/artfynd/A 35937-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5843163</v>
+        <v>73803941</v>
       </c>
       <c r="B2" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vårdinge, Näsbyhultet nära Frösjön, Srm</t>
+          <t>Näsbyhultet, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633666.2975563153</v>
+        <v>633799</v>
       </c>
       <c r="R2" t="n">
-        <v>6549063.29568616</v>
+        <v>6549173</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1976-08-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1976-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +768,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>strandskog</t>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,53 +796,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3145661</v>
+        <v>81883691</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vårdinge, Näsbyhultet nära Frösjön, Srm</t>
+          <t>Näsby nära grustaget på åsen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633666.2975563153</v>
+        <v>633751</v>
       </c>
       <c r="R3" t="n">
-        <v>6549063.29568616</v>
+        <v>6549196</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1976-08-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1976-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>strandskog</t>
+          <t>lövskog med asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,6 +904,521 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130243126</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Näsbyhultet, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>633745</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6549150</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3145661</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vårdinge, Näsbyhultet nära Frösjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>633666</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6549063</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1976-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1976-08-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>strandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>77814589</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fiskarstugan, 200 m NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633972</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6548938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-05-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123615353</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Näsbyhultet  nära vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633945</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6548963</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5843163</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vårdinge, Näsbyhultet nära Frösjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>633666</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6549063</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1976-08-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1976-08-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>strandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35937-2023 artfynd.xlsx
+++ b/artfynd/A 35937-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73803941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81883691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130243126</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3145661</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77814589</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123615353</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,8 +1454,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5843163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>